--- a/outputs/English Speaking Drill仕様書_v2.0.xlsx
+++ b/outputs/English Speaking Drill仕様書_v2.0.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>・不一致→「認証に失敗しました」
+          <t>・不一致→「認証に失敗しました(AUTH-002)」
 ・通信断→「サーバーに接続できません(NET-001)」</t>
         </is>
       </c>
@@ -3029,7 +3029,8 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5秒間隔でアクティビティを確認し、20秒無応答なら回復ダイアログを表示</t>
+          <t>5秒間隔でアクティビティを確認し、20秒無応答なら回復ダイアログを表示。
+タイマーのカウントダウン進行中はアクティブとみなす(回答待ちでの誤検知防止)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">

--- a/outputs/English Speaking Drill仕様書_v2.0.xlsx
+++ b/outputs/English Speaking Drill仕様書_v2.0.xlsx
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>・クリア時、または同一パートの挑戦回数が10回に到達で次のパートへ自動進行
+          <t>・クリア時、または同一パートの挑戦回数が3回に到達で次のパートへ自動進行
 ・usersシートの進捗を更新</t>
         </is>
       </c>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>REQUIRED_ATTEMPTS=10(要望No102/104対応)</t>
+          <t>REQUIRED_ATTEMPTS=3(要望No102/104対応、2026-08-11 Mukaさん依頼で10回→3回に変更)</t>
         </is>
       </c>
     </row>

--- a/outputs/English Speaking Drill仕様書_v2.0.xlsx
+++ b/outputs/English Speaking Drill仕様書_v2.0.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,28 @@
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>藤岡諒也</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>要望No.153〜186対応: ステージ解放10回→3回(No.152群/8-24)・ランキング表示名修正・SPAフォールバック追加(No.154)・タイマー/フリーズ検知の再設計(No.159/170/175/178/179/186)・readの文単位発音(No.155/182)・問題番号のデモ除外(No.166)・解放文言のadvanced連動(No.162)・マイク導線ヒント(No.161)・銃声音量0.1(No.167)・ログイン有効期限7日(No.169)・Tries表記(No.160)・認識候補の全件判定(No.176/180/185)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>藤岡諒也</t>
         </is>
@@ -1179,7 +1201,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>・トークン有効期限24時間
+          <t>・トークン有効期限7日(2026-08-30 要望No.169で24時間→7日に延長)
 ・ログイン試行回数の制限は未実装</t>
         </is>
       </c>
@@ -1382,7 +1404,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>・"read"は現在形/riːd/で発音(要望No138/142)
+          <t>・"read"は文単位で発音切替(既定/riːd/、過去形文は/red/・要望No.155/182)(要望No138/142)
 ・頭切れ対策(要望No143)</t>
         </is>
       </c>
@@ -1533,7 +1555,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>・効果音: attack.mp3/miss.mp3(音量0.2)</t>
+          <t>・効果音: attack.mp3(音量0.1・要望No.167で軽減)/miss.mp3(音量0.2)</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1699,8 @@
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>・保存失敗→エラー表示(結果画面へは遷移)
-・認証切れ→ログイン画面へ誘導</t>
+・認証切れ→ログイン画面へ誘導
+・API無応答は15秒でタイムアウト扱い(結果画面へは遷移)</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2099,7 +2122,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>・有効期限24h
+          <t>・有効期限7日(要望No.169)
 ・本番: secure+SameSite=None / 開発: SameSite=Lax</t>
         </is>
       </c>
@@ -2488,7 +2511,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>発音補正: read→/riːd/</t>
+          <t>発音補正: readは文単位で切替(既定は現在形/riːd/、PAST_READ_TEXTS該当文は過去形/red/・要望No.155/182)。Botchan/drank等の単語補正あり</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2911,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>回答受付開始で30秒カウントダウン。残10秒で赤表示。正解/停止で解除</t>
+          <t>回答受付開始で30秒カウントダウン。残10秒で赤表示。正解/停止で解除。表示は回答受付中のみ(前問の残り秒を引き継がない)</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -3030,7 +3053,8 @@
       <c r="D25" s="8" t="inlineStr">
         <is>
           <t>5秒間隔でアクティビティを確認し、20秒無応答なら回復ダイアログを表示。
-タイマーのカウントダウン進行中はアクティブとみなす(回答待ちでの誤検知防止)</t>
+タイマーのカウントダウン進行中・読み上げ/音声取得中・攻撃演出中はアクティブとみなす(誤検知防止)。
+タブ非表示中は判定せず、タイマーも一時停止する(復帰時に再開)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3171,7 +3195,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>クリア、または当該パートのプレイ回数≧10で次パートへ。partsを(学年,パート,サブパート)順に走査</t>
+          <t>クリア、または当該パートのプレイ回数≧3(REQUIRED_ATTEMPTS=3)で次パートへ。partsを(学年,パート,サブパート)順に走査</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -3595,14 +3619,17 @@
         <is>
           <t>・左上: Grade/Part/Subpart表示+「やめる」ボタン
 ・右上: マイク状態(🎤MIC:ON/🔇MIC:OFF)+「Heard: 認識文」
-・左: 問題番号/残り時間(残10秒で赤)
+・左: 問題番号(デモを除いた本問1〜7で数える。デモ問題は「デモ」表示)/残り時間(回答受付中のみ表示・残10秒で赤)
 ・上中央: 敵キャラ(通常/攻撃/撃破)
 ・開始前: Requirement(回答条件)パネル+Startボタン
 ・問題文(画像つき問題は左カラム表示)
 ・画像(右カラム 最大300×250px)
 ・銃ボタン(マイクON/OFF)
 ・正解表示パネル(緑+✓)
-・フリーズ回復ダイアログ(リトライ/次の問題へ/やめる)</t>
+・フリーズ回復ダイアログ(リトライ/次の問題へ/やめる)
+・回答受付中にマイクOFFのまま: ガンボタン上に「🎤 ガンボタンをおして こたえてね」のヒント表示
+・音声再生に失敗: 「音声を再生できませんでした/もういちど聞く」を表示(ゲームは続行)
+・最終問題の結果送信中: 「けっかを ほぞんしています…」のオーバーレイを表示(保存APIは15秒タイムアウトで必ず結果画面へ遷移)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -3621,7 +3648,7 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>・問題文テキストはバナー表示後すぐ表示し、音声を2回読み上げてから回答受付
-・バナー「start a demo !」「Question N !」を2秒表示
+・バナー「start a demo !」「Question N !」(Nはデモを除いた本問番号1〜7)を2秒表示
 ・デモ問題は自動進行</t>
         </is>
       </c>
@@ -3642,7 +3669,7 @@
           <t>・スコア(正解数/問題数と%)
 ・CLEAR/FAILEDバッジ
 ・メッセージ(Perfect!〜Try Again...)
-・クリア時「次のステージが解放されました！」
+・クリアかつ解放時「次のステージが解放されました！」(再クリアなど解放が起きない場合は「よくがんばりました！」・最終ステージクリアは「全ステージクリア！おめでとう！」)
 ・未クリア時「あと N 問正解でクリア！」
 ・LOGOUTボタン/NEXT(またはRetry)ボタン</t>
         </is>
@@ -3680,7 +3707,7 @@
         <is>
           <t>・タイトル「Ranking 👑」
 ・期間(当月)表示
-・Number of try(挑戦回数 上位3)
+・Tries(挑戦回数 上位3・要望No.160で表記変更)
 ・Best Scores(正答率 上位3)
 ・Backボタン</t>
         </is>

--- a/outputs/English Speaking Drill仕様書_v2.0.xlsx
+++ b/outputs/English Speaking Drill仕様書_v2.0.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -803,28 +803,6 @@
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>藤岡諒也</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>v2.1</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>要望No.153〜186対応: ステージ解放10回→3回(No.152群/8-24)・ランキング表示名修正・SPAフォールバック追加(No.154)・タイマー/フリーズ検知の再設計(No.159/170/175/178/179/186)・readの文単位発音(No.155/182)・問題番号のデモ除外(No.166)・解放文言のadvanced連動(No.162)・マイク導線ヒント(No.161)・銃声音量0.1(No.167)・ログイン有効期限7日(No.169)・Tries表記(No.160)・認識候補の全件判定(No.176/180/185)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>藤岡諒也</t>
         </is>
@@ -1201,7 +1179,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>・トークン有効期限7日(2026-08-30 要望No.169で24時間→7日に延長)
+          <t>・トークン有効期限24時間
 ・ログイン試行回数の制限は未実装</t>
         </is>
       </c>
@@ -1404,7 +1382,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>・"read"は文単位で発音切替(既定/riːd/、過去形文は/red/・要望No.155/182)(要望No138/142)
+          <t>・"read"は現在形/riːd/で発音(要望No138/142)
 ・頭切れ対策(要望No143)</t>
         </is>
       </c>
@@ -1555,7 +1533,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>・効果音: attack.mp3(音量0.1・要望No.167で軽減)/miss.mp3(音量0.2)</t>
+          <t>・効果音: attack.mp3/miss.mp3(音量0.2)</t>
         </is>
       </c>
     </row>
@@ -1699,8 +1677,7 @@
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>・保存失敗→エラー表示(結果画面へは遷移)
-・認証切れ→ログイン画面へ誘導
-・API無応答は15秒でタイムアウト扱い(結果画面へは遷移)</t>
+・認証切れ→ログイン画面へ誘導</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2122,7 +2099,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>・有効期限7日(要望No.169)
+          <t>・有効期限24h
 ・本番: secure+SameSite=None / 開発: SameSite=Lax</t>
         </is>
       </c>
@@ -2511,7 +2488,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>発音補正: readは文単位で切替(既定は現在形/riːd/、PAST_READ_TEXTS該当文は過去形/red/・要望No.155/182)。Botchan/drank等の単語補正あり</t>
+          <t>発音補正: read→/riːd/</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2888,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>回答受付開始で30秒カウントダウン。残10秒で赤表示。正解/停止で解除。表示は回答受付中のみ(前問の残り秒を引き継がない)</t>
+          <t>回答受付開始で30秒カウントダウン。残10秒で赤表示。正解/停止で解除</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -3053,8 +3030,7 @@
       <c r="D25" s="8" t="inlineStr">
         <is>
           <t>5秒間隔でアクティビティを確認し、20秒無応答なら回復ダイアログを表示。
-タイマーのカウントダウン進行中・読み上げ/音声取得中・攻撃演出中はアクティブとみなす(誤検知防止)。
-タブ非表示中は判定せず、タイマーも一時停止する(復帰時に再開)</t>
+タイマーのカウントダウン進行中はアクティブとみなす(回答待ちでの誤検知防止)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3195,7 +3171,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>クリア、または当該パートのプレイ回数≧3(REQUIRED_ATTEMPTS=3)で次パートへ。partsを(学年,パート,サブパート)順に走査</t>
+          <t>クリア、または当該パートのプレイ回数≧10で次パートへ。partsを(学年,パート,サブパート)順に走査</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -3619,17 +3595,14 @@
         <is>
           <t>・左上: Grade/Part/Subpart表示+「やめる」ボタン
 ・右上: マイク状態(🎤MIC:ON/🔇MIC:OFF)+「Heard: 認識文」
-・左: 問題番号(デモを除いた本問1〜7で数える。デモ問題は「デモ」表示)/残り時間(回答受付中のみ表示・残10秒で赤)
+・左: 問題番号/残り時間(残10秒で赤)
 ・上中央: 敵キャラ(通常/攻撃/撃破)
 ・開始前: Requirement(回答条件)パネル+Startボタン
 ・問題文(画像つき問題は左カラム表示)
 ・画像(右カラム 最大300×250px)
 ・銃ボタン(マイクON/OFF)
 ・正解表示パネル(緑+✓)
-・フリーズ回復ダイアログ(リトライ/次の問題へ/やめる)
-・回答受付中にマイクOFFのまま: ガンボタン上に「🎤 ガンボタンをおして こたえてね」のヒント表示
-・音声再生に失敗: 「音声を再生できませんでした/もういちど聞く」を表示(ゲームは続行)
-・最終問題の結果送信中: 「けっかを ほぞんしています…」のオーバーレイを表示(保存APIは15秒タイムアウトで必ず結果画面へ遷移)</t>
+・フリーズ回復ダイアログ(リトライ/次の問題へ/やめる)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -3648,7 +3621,7 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>・問題文テキストはバナー表示後すぐ表示し、音声を2回読み上げてから回答受付
-・バナー「start a demo !」「Question N !」(Nはデモを除いた本問番号1〜7)を2秒表示
+・バナー「start a demo !」「Question N !」を2秒表示
 ・デモ問題は自動進行</t>
         </is>
       </c>
@@ -3669,7 +3642,7 @@
           <t>・スコア(正解数/問題数と%)
 ・CLEAR/FAILEDバッジ
 ・メッセージ(Perfect!〜Try Again...)
-・クリアかつ解放時「次のステージが解放されました！」(再クリアなど解放が起きない場合は「よくがんばりました！」・最終ステージクリアは「全ステージクリア！おめでとう！」)
+・クリア時「次のステージが解放されました！」
 ・未クリア時「あと N 問正解でクリア！」
 ・LOGOUTボタン/NEXT(またはRetry)ボタン</t>
         </is>
@@ -3707,7 +3680,7 @@
         <is>
           <t>・タイトル「Ranking 👑」
 ・期間(当月)表示
-・Tries(挑戦回数 上位3・要望No.160で表記変更)
+・Number of try(挑戦回数 上位3)
 ・Best Scores(正答率 上位3)
 ・Backボタン</t>
         </is>
